--- a/data/batches/B12_TrialDesign_TA_TE_TI_TV_TD/Test_Validation_Report/Test_Validation_Report_B12.xlsx
+++ b/data/batches/B12_TrialDesign_TA_TE_TI_TV_TD/Test_Validation_Report/Test_Validation_Report_B12.xlsx
@@ -771,7 +771,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -822,7 +822,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1466,57 +1466,57 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Audit Row Index</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>CSV Row Index Checked</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Original Value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Actual Original Value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Injected Value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Actual Dirty Value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Original Match</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Dirty Match</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Original and Dirty csv imputation match</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Validation Status</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Comments</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Audit Row Index</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Original Value</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Actual Original Value</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Injected Value</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Actual Dirty Value</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Original Match</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Dirty Match</t>
         </is>
       </c>
     </row>
@@ -1541,41 +1541,63 @@
           <t>TE</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+          <t>Complete Row @ CSV Row 2; count=1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 2; count=2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Duplicate row injection verified successfully</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1598,41 +1620,37 @@
           <t>TE</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
         <v>5</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>USUBJID column missing for duplicate row validation</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Row index 3 is out of bounds (Original TE.csv has 3 rows)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1655,41 +1673,37 @@
           <t>TE</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>ETCD</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
         <v>5</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Row index out of range</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Row index out of range</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1712,65 +1726,61 @@
           <t>TE</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>ETCD</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
         <v>4</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>TRT</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TRT</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ZZZSD1379</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>ZZZSD1379</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Imputation verified successfully</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>TRT</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>TRT</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>ZZZSD1379</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>ZZZSD1379</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1795,41 +1805,63 @@
           <t>TA</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
         <v>4</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 4; count=1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 4; count=1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>USUBJID column missing for duplicate row validation</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Duplicate row injection mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1852,41 +1884,37 @@
           <t>TA</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>TAETORD</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
         <v>8</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Row index out of range</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Row index out of range</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1909,65 +1937,61 @@
           <t>TA</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>ARMCD</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>NBI_1065846</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>NBI_1065846</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ZZZSD1354</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>ZZZSD1354</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Imputation verified successfully</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>NBI_1065846</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>NBI_1065846</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>ZZZSD1354</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>ZZZSD1354</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1992,41 +2016,63 @@
           <t>TI</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="n">
         <v>8</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+          <t>Complete Row @ CSV Row 8; count=1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 8; count=2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Duplicate row injection verified successfully</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2049,65 +2095,61 @@
           <t>TA</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>ARMCD</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
         <v>3</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>NBI_1065846</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>NBI_1065846</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SCRNFAIL</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>SCRNFAIL</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Imputation verified successfully</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>NBI_1065846</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>NBI_1065846</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>SCRNFAIL</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>SCRNFAIL</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2132,65 +2174,61 @@
           <t>TV</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>ARMCD</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
         <v>3</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>NBI_1065846</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>NBI_1065846</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SCRNFAIL</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>SCRNFAIL</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Imputation verified successfully</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>NBI_1065846</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>NBI_1065846</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>SCRNFAIL</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>SCRNFAIL</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2215,65 +2253,61 @@
           <t>TV</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>ARMCD</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>11</v>
+      </c>
+      <c r="H12" t="n">
         <v>13</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>PLACEBO</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>PLACEBO</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SCRNFAIL</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>SCRNFAIL</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Imputation verified successfully</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>PLACEBO</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>PLACEBO</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>SCRNFAIL</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>SCRNFAIL</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3254,10 +3288,10 @@
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -3272,7 +3306,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>33.33</v>
+        <v>55.56</v>
       </c>
     </row>
   </sheetData>
